--- a/public/templates/template_siswa.xlsx
+++ b/public/templates/template_siswa.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>nipd</t>
   </si>
@@ -77,7 +77,7 @@
     <t>2024-05-21</t>
   </si>
   <si>
-    <t>KETERANGAN:</t>
+    <t>BACA KETERANGAN!!! :</t>
   </si>
   <si>
     <t>- nipd: Username (wajib, unique, max 9)</t>
@@ -95,7 +95,10 @@
     <t>- Hapus baris 2 sebelum import!</t>
   </si>
   <si>
-    <t>- Disarankan menggunakan spreadsheet dibanding excel</t>
+    <t>- Disarankan menggunakan SPREADSHEET</t>
+  </si>
+  <si>
+    <t>- !!!(FORMAT SEMUA COLUMN MENJADI TEKS BIASA)</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="true" style="0"/>
@@ -584,6 +587,11 @@
         <v>26</v>
       </c>
     </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
